--- a/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:19:25+00:00</t>
+    <t>2026-10-13T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T06:32:12+00:00</t>
+    <t>2026-10-13T12:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="118">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,6 +276,12 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -929,10 +935,10 @@
         <v>86</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -992,10 +998,10 @@
         <v>85</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>21</v>
@@ -1003,10 +1009,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1017,7 +1023,7 @@
         <v>84</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>21</v>
@@ -1029,13 +1035,13 @@
         <v>21</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1086,13 +1092,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -1101,15 +1107,15 @@
         <v>21</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1132,13 +1138,13 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1177,19 +1183,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>84</v>
@@ -1201,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -1209,10 +1215,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1220,10 +1226,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1235,16 +1241,16 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1294,13 +1300,13 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
@@ -1309,15 +1315,15 @@
         <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1325,10 +1331,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -1340,13 +1346,13 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1373,11 +1379,11 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -1395,22 +1401,22 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
